--- a/data/google_news_dedup_audit_29_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_29_0426_UTC.xlsx
@@ -445,10 +445,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>0.4852896928787231</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>0.5387002825737</v>
@@ -487,10 +487,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>0.4943191707134247</v>
@@ -508,10 +508,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>0.4746301174163818</v>
@@ -529,10 +529,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>0.4574146270751953</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
         <v>0.7571534514427185</v>
@@ -571,10 +571,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>0.3685643076896667</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>0.4968286156654358</v>
@@ -613,13 +613,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4054416418075562</v>
+        <v>0.5603243112564087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -628,19 +628,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2 Jews injured in stabbing attack in London's Golders Green, says emergency response group - The Times of Israel</t>
+          <t>UK leaders condemn stabbing of two Jews in London amid rising antisemitic incidents - ynetnews</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4732542634010315</v>
+        <v>0.4054416418075562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Two stabbed in Golders Green, north-west London, says Jewish group - The Guardian</t>
+          <t>2 Jews injured in stabbing attack in London's Golders Green, says emergency response group - The Times of Israel</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5603243112564087</v>
+        <v>0.4732542634010315</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -670,16 +670,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UK leaders condemn stabbing of two Jews in London amid rising antisemitic incidents - ynetnews</t>
+          <t>Two stabbed in Golders Green, north-west London, says Jewish group - The Guardian</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
         <v>0.4531742334365845</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4674909114837646</v>
+        <v>0.4674909710884094</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
         <v>0.5155401825904846</v>
@@ -739,10 +739,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
         <v>0.6917082071304321</v>
@@ -760,10 +760,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
         <v>0.7488348484039307</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
         <v>0.6557744741439819</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
         <v>0.5837048292160034</v>
@@ -823,10 +823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" t="n">
         <v>0.4963404536247253</v>
@@ -844,10 +844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" t="n">
         <v>0.3627550601959229</v>
@@ -865,10 +865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C22" t="n">
         <v>0.9999999403953552</v>
